--- a/対応管理表.xlsx
+++ b/対応管理表.xlsx
@@ -1441,7 +1441,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1464,6 +1464,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFFDE9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1617,7 +1623,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1625,7 +1631,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1894,7 +1900,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFFDE9E7"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1908,7 +1914,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFDE9E7"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -10765,7 +10771,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -11097,7 +11103,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -11108,7 +11114,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -11260,7 +11266,7 @@
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -11271,14 +11277,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="B1:C36"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11286,46 +11292,40 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
+    <row r="2" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C2" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="25"/>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25" t="s">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C5" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="25"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C7" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="25"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="25"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="26" t="s">
@@ -11340,7 +11340,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="27" t="s">
         <v>91</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="27" t="s">
         <v>96</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="27" t="s">
         <v>98</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="27" t="s">
         <v>11</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="27" t="s">
         <v>12</v>
       </c>
@@ -11470,53 +11470,35 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="25" t="s">
+    <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C32" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="25"/>
-    </row>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="25" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C33" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="25"/>
-    </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="25" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="25"/>
-    </row>
-    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="25" t="s">
+    </row>
+    <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C35" s="25"/>
-    </row>
-    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="25" t="s">
+    </row>
+    <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C36" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
